--- a/client-docs/HCC-Jobs-Review.xlsx
+++ b/client-docs/HCC-Jobs-Review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jobs'!$A$1:$Q$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jobs'!$A$1:$R$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>7. Grey columns are for reference. Please don't change "Job ref": it links each row to its advert.</t>
+          <t>7. Grey columns are for reference. Please don't change "Job ref" or "Web address": they link each row to its advert.</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,8 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -707,6 +708,11 @@
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
+          <t>Web address (do not change)</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
           <t>Description (optional to edit)</t>
         </is>
       </c>
@@ -774,7 +780,12 @@
           <t>HCC-W11618</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>care-home-chef-agency-chef-jobs-in-maryport-ca15-cumbria</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>Care Home Chef Jobs in Maryport, CA15 
   Are you an experienced Care Home Chef looking for flexible chef work in Maryport, CA15 or the surrounding Cumbria area?  
@@ -868,7 +879,12 @@
           <t>HCC-W11605</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>registered-staff-nurse-rgn-birmingham-solihull-b90</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>HCC-Temps Staffing | Registered Nurse Jobs | Staff Nurse Jobs | Agency Nursing | Birmingham &amp; Solihull  
  Job Description 
@@ -971,7 +987,12 @@
           <t>HCC-W11588</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>senior-carer-senior-care-assistant-agency-work-basingstoke</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Carer Jobs in Basingstoke 
  We are currently recruiting an experienced  Senior Carer / Senior Care Assistant  to work regular agency shifts with our client in  Basingstoke, Hampshire (RG21) . 
@@ -1082,7 +1103,12 @@
           <t>HCC-W6609</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>school-kitchen-assistant-hospitality-temp-agency</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>School Kitchen Assistant (Hospitality Temp Agency) Jobs in Clacton-on-Sea, CO16 
   Looking for flexible, rewarding work in school kitchens?  
@@ -1184,7 +1210,12 @@
           <t>HCC-W6380</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>temp-barista-in-london</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>Job Description:   
  Are you a skilled barista with a passion for creating excellent coffee and delivering top-notch customer service? We are looking for an enthusiastic and dedicated barista to join our team in London. If you thrive in a fast-paced environment and enjoy working with people, this is the perfect opportunity for you! 
@@ -1284,7 +1315,12 @@
           <t>HCC-W6224</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-lymington-so41-urgent</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Lymington. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -1380,7 +1416,12 @@
           <t>HCC-W6223</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-catford-se6-urgent</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Catford, London. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -1475,7 +1516,12 @@
           <t>HCC-W6209</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>christmas-temp-chef-jobs-in-newcastle-ne20</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>Temp Chef Jobs in Newcastle, NE20  
   Join HCC-Temps and Take Your Skills to the Next Kitchen  
@@ -1578,7 +1624,12 @@
           <t>HCC-W6208</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-staffordshire-ws11-urgent</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Staffordshire. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -1674,7 +1725,12 @@
           <t>HCC-W6131</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-portsmouth</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Join Portmouth’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -1774,7 +1830,12 @@
           <t>HCC-W6130</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-southampton</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>Join Southampton’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -1874,7 +1935,12 @@
           <t>HCC-W6129</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-southampton-2</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>Healthcare Assistant Jobs in Southampton –  Start Your Career with HCC-Temps  
  Are you searching for  Healthcare Assistant jobs in Southampton  that offer flexibility, competitive pay, and a supportive work environment? 
@@ -1975,7 +2041,12 @@
           <t>HCC-W6128</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>Healthcare Assistant Jobs in Portsmouth –  Start Your Career with HCC-Temps  
  Are you searching for  Healthcare Assistant jobs in Portsmouth  that offer flexibility, competitive pay, and a supportive work environment? 
@@ -2076,7 +2147,12 @@
           <t>HCC-W5876</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-sevenoaks</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>Join Sevenoak’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -2176,7 +2252,12 @@
           <t>HCC-W5875</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-suffolk</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>Join Suffolk’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -2276,7 +2357,12 @@
           <t>HCC-W5874</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-kent</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>Join Kent’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -2376,7 +2462,12 @@
           <t>HCC-W5873</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-essex</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>Join Essex’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -2476,7 +2567,12 @@
           <t>HCC-W5871</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistants-needed-east-sussex</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>Join East Sussex’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
  Are you ready to kickstart or grow your career in hospitality? 
@@ -2575,7 +2671,12 @@
           <t>HCC-W5854</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-hartlepool-ts25</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>Temp Chef Jobs in Consett, DH8 – Join HCC-Temps Today  
  Are you searching for  Temp Chef jobs in Consett, DH8  that offer flexibility, excellent pay, and the chance to cook in a variety of kitchens? 
@@ -2675,7 +2776,12 @@
           <t>HCC-W5852</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-somerset-ta4-needed-today-2</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>Temp Chef Needed in Hartlepool, TS25 – Join HCC-Temps Today!  
  Are you searching for  Temp Chef jobs in Hartlepool, TS25  with excellent pay, flexible shifts, and the chance to work in diverse and exciting kitchens? 
@@ -2776,7 +2882,12 @@
           <t>HCC-W5047</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>hospitality-agency-housekeepers-needed-today</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>Domestic Assistant Jobs in Southampton, SO45 – Work with a Leading Hospitality Agency  
  Looking for flexible, rewarding work in the hospitality sector?  
@@ -2877,7 +2988,12 @@
           <t>HCC-W5036</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>hospitality-agency-housekeepers-needed</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>Portsmouth’s Leading Hospitality Agency – Housekeepers Needed!  
  Join Portsmouth’s top hospitality agency! Flexible Housekeeping jobs, great pay, weekly wages, and exciting venues. Apply today! 
@@ -2978,7 +3094,12 @@
           <t>HCC-W5032</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-somerset-ta4-needed-today</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>Temp Chef Jobs in Somerset, TA4  
   Join HCC-Temps and Take Your Skills to the Next Kitchen  
@@ -3080,7 +3201,12 @@
           <t>HCC-W5030</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-derby-de72</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>Temp Chef Jobs in Derby, DE67   
   Your Next Opportunity with HCC-Temps    
@@ -3181,7 +3307,12 @@
           <t>HCC-W5027</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-berkshire</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>Temp Chef Jobs in Berkshire, SL6 – Join HCC-Temps and   
   Cook Up Your Next Career Move!  
@@ -3283,7 +3414,12 @@
           <t>HCC-W5018</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-letcombe-regis</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>Healthcare Assistant Jobs in Letcombe Regis –  Start Your Career with HCC-Temps  
  Are you searching for  Healthcare Assistant jobs in Letcombe Regis  that offer flexibility, competitive pay, and a supportive work environment? 
@@ -3384,7 +3520,12 @@
           <t>HCC-W5013</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>hospitality-agency-kitchen-asst-needed</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>Ke  nt’s Leading Hospitality Agency – Kitchen Assistant Needed!  
  Join Kent’s top hospitality agency! Flexible kitchen assistant jobs, great pay, weekly wages, and exciting venues. Apply today! 
@@ -3485,7 +3626,12 @@
           <t>HCC-W3756</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-norwich-nr1-urgent</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Norwich. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -3581,7 +3727,12 @@
           <t>HCC-W3748</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-bristol-bs1-urgent</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Bristol. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -3677,7 +3828,12 @@
           <t>HCC-W3747</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-grays-rm20-urgent</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Grays. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -3773,7 +3929,12 @@
           <t>HCC-W3746</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-west-yorkshire-ls1-urgent</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in West Yorkshire. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -3863,7 +4024,12 @@
           <t>HCC-W3744</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>temp-healthcare-assistant-in-gloucester-urgent</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -3966,7 +4132,12 @@
           <t>HCC-W3743</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>temp-kitchen-assistants-in-gloucester-urgent</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Gloucester. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -4069,7 +4240,12 @@
           <t>HCC-W3741</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-wigan-urgent</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Wigan. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -4165,7 +4341,12 @@
           <t>HCC-W3740</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-with-dbs-in-taunton-somerset-urgent</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Taunton. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -4261,7 +4442,12 @@
           <t>HCC-W3739</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-sheffield-urgent</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Sheffield. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -4356,7 +4542,12 @@
           <t>HCC-W3348</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>temp-registered-nurse-in-london</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Nurse seeking flexible work with competitive pay? Join HCC-Temps, where your clinical expertise and compassion are highly valued. We’re looking for dedicated nurses to support our clients in various healthcare settings across London. 
@@ -4457,7 +4648,12 @@
           <t>HCC-W3110</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-portsmouth</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>Job Overview 
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Portsmouth, working in a range of settings, including care homes, corporate venues, and more. 
@@ -4557,7 +4753,12 @@
           <t>HCC-W3107</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-southampton</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>Job Overview 
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Southampton, working in a range of settings, including care homes, corporate venues, and more. 
@@ -4658,7 +4859,12 @@
           <t>HCC-W2534</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>temp-barista-in-leicester</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>Job Description:   
  Are you a skilled barista with a passion for creating excellent coffee and delivering top-notch customer service? We are looking for an enthusiastic and dedicated barista to join our team in Leicester. If you thrive in a fast-paced environment and enjoy working with people, this is the perfect opportunity for you! 
@@ -4758,7 +4964,12 @@
           <t>HCC-W2533</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>temp-bartender-in-leicester</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled bartender looking for flexible shifts and a supportive work environment? Join HCC-Temps and put your bartending expertise to use in a variety of settings. We’re seeking motivated and friendly bartenders to provide excellent service to our clients in Leicester. 
@@ -4857,7 +5068,12 @@
           <t>HCC-W2532</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-leicester</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Leicester. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -4952,7 +5168,12 @@
           <t>HCC-W2531</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>temp-registered-nurse-in-leicester</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Nurse seeking flexible work with competitive pay? Join HCC-Temps, where your clinical expertise and compassion are highly valued. We’re looking for dedicated nurses to support our clients in various healthcare settings across Leicester. 
@@ -5048,7 +5269,12 @@
           <t>HCC-W2530</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>temp-healthcare-assistant-in-leicester</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -5151,7 +5377,12 @@
           <t>HCC-W2529</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>temp-hospitality-assistant-in-leicester</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for flexible work in the hospitality industry? Join HCC-Temps, where your dedication and skills are truly appreciated. We are currently seeking a reliable Hospitality Assistant to support our clients in Leicester, offering a range of work across different settings. 
@@ -5253,7 +5484,12 @@
           <t>HCC-W2528</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>temp-kitchen-assistants-in-leicester</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Leicester. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -5355,7 +5591,12 @@
           <t>HCC-W2527</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-leicester</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Leicester, working in a range of settings, including care homes, corporate venues, and more. 
@@ -5458,7 +5699,12 @@
           <t>HCC-W2526</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
+          <t>temp-barista-in-derby</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>Job Description:   
  Are you a skilled barista with a passion for creating excellent coffee and delivering top-notch customer service? We are looking for an enthusiastic and dedicated barista to join our team in Bath. If you thrive in a fast-paced environment and enjoy working with people, this is the perfect opportunity for you! 
@@ -5558,7 +5804,12 @@
           <t>HCC-W2525</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="10" t="inlineStr">
+        <is>
+          <t>temp-bartender-in-bath</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled bartender looking for flexible shifts and a supportive work environment? Join HCC-Temps and put your bartending expertise to use in a variety of settings. We’re seeking motivated and friendly bartenders to provide excellent service to our clients in Bath. 
@@ -5657,7 +5908,12 @@
           <t>HCC-W2524</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="10" t="inlineStr">
+        <is>
+          <t>temp-cleaner-in-bath</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Bath. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -5752,7 +6008,12 @@
           <t>HCC-W2523</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="10" t="inlineStr">
+        <is>
+          <t>temp-registered-nurse-in-bath</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Nurse seeking flexible work with competitive pay? Join HCC-Temps, where your clinical expertise and compassion are highly valued. We’re looking for dedicated nurses to support our clients in various healthcare settings across Bath. 
@@ -5848,7 +6109,12 @@
           <t>HCC-W2522</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
+          <t>temp-healthcare-assistant-in-bath</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -5951,7 +6217,12 @@
           <t>HCC-W2519</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
+          <t>temp-hospitality-assistant-in-bath</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for flexible work in the hospitality industry? Join HCC-Temps, where your dedication and skills are truly appreciated. We are currently seeking a reliable Hospitality Assistant to support our clients in Bath, offering a range of work across different settings. 
@@ -6053,7 +6324,12 @@
           <t>HCC-W2349</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="10" t="inlineStr">
+        <is>
+          <t>temp-kitchen-assistants-in-bath</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Bath. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -6155,7 +6431,12 @@
           <t>HCC-W2348</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
+          <t>temp-chef-jobs-in-bath</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Bath, working in a range of settings, including care homes, corporate venues, and more. 
@@ -6258,7 +6539,12 @@
           <t>HCC-W2322</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
+          <t>bartender-derby</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled bartender looking for flexible shifts and a supportive work environment? Join HCC-Temps and put your bartending expertise to use in a variety of settings. We’re seeking motivated and friendly bartenders to provide excellent service to our clients in Derby. 
@@ -6357,7 +6643,12 @@
           <t>HCC-W2320</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="10" t="inlineStr">
+        <is>
+          <t>barista-derby</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>Job Description:   
  Are you a skilled barista with a passion for creating excellent coffee and delivering top-notch customer service? We are looking for an enthusiastic and dedicated barista to join our team in Derby. If you thrive in a fast-paced environment and enjoy working with people, this is the perfect opportunity for you! 
@@ -6456,7 +6747,12 @@
           <t>HCC-W2319</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="10" t="inlineStr">
+        <is>
+          <t>registered-nurse-derby</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Nurse seeking flexible work with competitive pay? Join HCC-Temps, where your clinical expertise and compassion are highly valued. We’re looking for dedicated nurses to support our clients in various healthcare settings across Derby. 
@@ -6552,7 +6848,12 @@
           <t>HCC-W2318</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-derby</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -6655,7 +6956,12 @@
           <t>HCC-W2317</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="10" t="inlineStr">
+        <is>
+          <t>cleaner-derby</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Derby. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -6751,7 +7057,12 @@
           <t>HCC-W2316</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="10" t="inlineStr">
+        <is>
+          <t>hospitality-assistant-derby</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for flexible work in the hospitality industry? Join HCC-Temps, where your dedication and skills are truly appreciated. We are currently seeking a reliable Hospitality Assistant to support our clients in Derby, offering a range of work across different settings. 
@@ -6853,7 +7164,12 @@
           <t>HCC-W2314</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
+      <c r="Q63" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistant-derby</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Derby. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -6955,7 +7271,12 @@
           <t>HCC-W2313</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
+      <c r="Q64" s="10" t="inlineStr">
+        <is>
+          <t>chef-derby</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Derby, working in a range of settings, including care homes, corporate venues, and more. 
@@ -7052,7 +7373,12 @@
           <t>HCC-W2288</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="inlineStr">
+      <c r="Q65" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-southampton</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -7151,7 +7477,12 @@
           <t>HCC-W2241</t>
         </is>
       </c>
-      <c r="Q66" s="6" t="inlineStr">
+      <c r="Q66" s="10" t="inlineStr">
+        <is>
+          <t>cleaner-cheshire</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a reliable and detail-oriented cleaner looking for flexible work? Join HCC-Temps and become part of our professional team in Cheshire. We’re seeking experienced cleaners to maintain high standards of cleanliness across various locations. 
@@ -7243,7 +7574,12 @@
           <t>HCC-W2240</t>
         </is>
       </c>
-      <c r="Q67" s="6" t="inlineStr">
+      <c r="Q67" s="10" t="inlineStr">
+        <is>
+          <t>bartender-cheshire</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled bartender looking for flexible shifts and a supportive work environment? Join HCC-Temps and put your bartending expertise to use in a variety of settings. We’re seeking motivated and friendly bartenders to provide excellent service to our clients in Cheshire. 
@@ -7342,7 +7678,12 @@
           <t>HCC-W2239</t>
         </is>
       </c>
-      <c r="Q68" s="6" t="inlineStr">
+      <c r="Q68" s="10" t="inlineStr">
+        <is>
+          <t>barista-cheshire</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
         <is>
           <t>Job Description:   
  Are you a skilled barista with a passion for creating excellent coffee and delivering top-notch customer service? We are looking for an enthusiastic and dedicated barista to join our team in Cheshire. If you thrive in a fast-paced environment and enjoy working with people, this is the perfect opportunity for you! 
@@ -7441,7 +7782,12 @@
           <t>HCC-W2238</t>
         </is>
       </c>
-      <c r="Q69" s="6" t="inlineStr">
+      <c r="Q69" s="10" t="inlineStr">
+        <is>
+          <t>registered-nurse-cheshire</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Nurse seeking flexible work with competitive pay? Join HCC-Temps, where your clinical expertise and compassion are highly valued. We’re looking for dedicated nurses to support our clients in various healthcare settings across Cheshire. 
@@ -7543,7 +7889,12 @@
           <t>HCC-W2237</t>
         </is>
       </c>
-      <c r="Q70" s="6" t="inlineStr">
+      <c r="Q70" s="10" t="inlineStr">
+        <is>
+          <t>hospitality-assistant-cheshire</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for flexible work in the hospitality industry? Join HCC-Temps, where your dedication and skills are truly appreciated. We are currently seeking a reliable Hospitality Assistant to support our clients in Cheshire, offering a range of work across different settings. 
@@ -7645,7 +7996,12 @@
           <t>HCC-W2236</t>
         </is>
       </c>
-      <c r="Q71" s="6" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistant-cheshire</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Cheshire. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -7747,7 +8103,12 @@
           <t>HCC-W2235</t>
         </is>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
+      <c r="Q72" s="10" t="inlineStr">
+        <is>
+          <t>chef-cheshire</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Cheshire, working in a range of settings, including care homes, corporate venues, and more. 
@@ -7844,7 +8205,12 @@
           <t>HCC-W2234</t>
         </is>
       </c>
-      <c r="Q73" s="6" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-cheshire</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -7941,7 +8307,12 @@
           <t>HCC-W2190</t>
         </is>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
+      <c r="Q74" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-birmingham</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -8043,7 +8414,12 @@
           <t>HCC-W2172</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr">
+        <is>
+          <t>chef-northampton</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Northampton, working in a range of settings, including care homes, corporate venues, and more. 
@@ -8142,7 +8518,12 @@
           <t>HCC-W2164</t>
         </is>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
+      <c r="Q76" s="10" t="inlineStr">
+        <is>
+          <t>bartender-luton</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled bartender looking for flexible shifts and a supportive work environment? Join HCC-Temps and put your bartending expertise to use in a variety of settings. We’re seeking motivated and friendly bartenders to provide excellent service to our clients in Luton. 
@@ -8241,7 +8622,12 @@
           <t>HCC-W2162</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr">
+        <is>
+          <t>barista-luton</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
         <is>
           <t>Job Description:   
  Are you a skilled barista with a passion for creating excellent coffee and delivering top-notch customer service? We are looking for an enthusiastic and dedicated barista to join our team in Luton. If you thrive in a fast-paced environment and enjoy working with people, this is the perfect opportunity for you! 
@@ -8341,7 +8727,12 @@
           <t>HCC-W2161</t>
         </is>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
+      <c r="Q78" s="10" t="inlineStr">
+        <is>
+          <t>hospitality-assistant-luton</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for flexible work in the hospitality industry? Join HCC-Temps, where your dedication and skills are truly appreciated. We are currently seeking a reliable Hospitality Assistant to support our clients in Luton, offering a range of work across different settings. 
@@ -8443,7 +8834,12 @@
           <t>HCC-W2160</t>
         </is>
       </c>
-      <c r="Q79" s="6" t="inlineStr">
+      <c r="Q79" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistant-luton</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Luton. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -8545,7 +8941,12 @@
           <t>HCC-W2159</t>
         </is>
       </c>
-      <c r="Q80" s="6" t="inlineStr">
+      <c r="Q80" s="10" t="inlineStr">
+        <is>
+          <t>chef-luton</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Luton, working in a range of settings, including care homes, corporate venues, and more. 
@@ -8647,7 +9048,12 @@
           <t>HCC-W2157</t>
         </is>
       </c>
-      <c r="Q81" s="6" t="inlineStr">
+      <c r="Q81" s="10" t="inlineStr">
+        <is>
+          <t>registered-nurse-glasgow</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Nurse seeking flexible work with competitive pay? Join HCC-Temps, where your clinical expertise and compassion are highly valued. We’re looking for dedicated nurses to support our clients in various healthcare settings across Glasgow. 
@@ -8749,7 +9155,12 @@
           <t>HCC-W2154</t>
         </is>
       </c>
-      <c r="Q82" s="6" t="inlineStr">
+      <c r="Q82" s="10" t="inlineStr">
+        <is>
+          <t>cleaner-housekeeping-glasgow</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a dedicated cleaner looking for flexible work opportunities? Join  HCC-Temps , where your attention to detail and hard work are truly valued. We’re seeking reliable cleaners to support clients in Glasgow, working in various settings, including care homes, offices, and other professional environments. 
@@ -8852,7 +9263,12 @@
           <t>HCC-W2150</t>
         </is>
       </c>
-      <c r="Q83" s="6" t="inlineStr">
+      <c r="Q83" s="10" t="inlineStr">
+        <is>
+          <t>kitchen-assistant-glasgow</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you looking for a flexible role in a dynamic kitchen environment? Join  HCC-Temps  as a Kitchen Assistant and play a vital role in supporting culinary teams in Glasgow. We’re seeking reliable and enthusiastic individuals to assist with food preparation and ensure the smooth running of kitchen operations. 
@@ -8954,7 +9370,12 @@
           <t>HCC-W2149</t>
         </is>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
+      <c r="Q84" s="10" t="inlineStr">
+        <is>
+          <t>chef-glasgow</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you a skilled chef seeking flexible work opportunities? Join  HCC-Temps , where your culinary expertise is appreciated and rewarded. We’re looking for experienced chefs to support clients in Glasgow, working in a range of settings, including care homes, corporate venues, and more. 
@@ -9051,7 +9472,12 @@
           <t>HCC-W2148</t>
         </is>
       </c>
-      <c r="Q85" s="6" t="inlineStr">
+      <c r="Q85" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-glasgow</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -9148,7 +9574,12 @@
           <t>HCC-W2095</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="inlineStr">
+      <c r="Q86" s="10" t="inlineStr">
+        <is>
+          <t>healthcare-assistant-frome</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
         <is>
           <t>Job Description:  
  Are you an experienced Healthcare Assistant looking for flexible work? Join HCC-Temps, where your skills and compassion are valued. We’re seeking dedicated HCAs to support our clients across a variety of healthcare settings. 
@@ -9188,7 +9619,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q86"/>
+  <autoFilter ref="A1:R86"/>
   <dataValidations count="6">
     <dataValidation sqref="A2:A86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Live,Closed"</formula1>
